--- a/artfynd/A 12962-2024 artfynd.xlsx
+++ b/artfynd/A 12962-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113725</v>
+        <v>125113775</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454746</v>
+        <v>454618</v>
       </c>
       <c r="R2" t="n">
-        <v>6992129</v>
+        <v>6992151</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125113711</v>
+        <v>125113717</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454543</v>
+        <v>454766</v>
       </c>
       <c r="R4" t="n">
-        <v>6992277</v>
+        <v>6992229</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113722</v>
+        <v>125113720</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454752</v>
+        <v>454770</v>
       </c>
       <c r="R5" t="n">
-        <v>6992152</v>
+        <v>6992167</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113724</v>
+        <v>125113721</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454720</v>
+        <v>454767</v>
       </c>
       <c r="R6" t="n">
-        <v>6992151</v>
+        <v>6992161</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1307,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125113706</v>
+        <v>125113718</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454605</v>
+        <v>454741</v>
       </c>
       <c r="R8" t="n">
-        <v>6992025</v>
+        <v>6992287</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125113718</v>
+        <v>125113722</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454741</v>
+        <v>454752</v>
       </c>
       <c r="R9" t="n">
-        <v>6992287</v>
+        <v>6992152</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125113721</v>
+        <v>125113785</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454767</v>
+        <v>454747</v>
       </c>
       <c r="R10" t="n">
-        <v>6992161</v>
+        <v>6992042</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,11 +1597,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,7 +1623,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125113720</v>
+        <v>125113707</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1668,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454770</v>
+        <v>454599</v>
       </c>
       <c r="R11" t="n">
-        <v>6992167</v>
+        <v>6992080</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113728</v>
+        <v>125113780</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454803</v>
+        <v>454741</v>
       </c>
       <c r="R12" t="n">
-        <v>6991945</v>
+        <v>6992267</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,11 +1806,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,7 +1832,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113707</v>
+        <v>125113709</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1882,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454599</v>
+        <v>454627</v>
       </c>
       <c r="R13" t="n">
-        <v>6992080</v>
+        <v>6992167</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1949,7 +1939,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113701</v>
+        <v>125113726</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -1989,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454753</v>
+        <v>454737</v>
       </c>
       <c r="R14" t="n">
-        <v>6991908</v>
+        <v>6992033</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2056,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125113727</v>
+        <v>125113705</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2096,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454754</v>
+        <v>454690</v>
       </c>
       <c r="R15" t="n">
-        <v>6992018</v>
+        <v>6991954</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2126,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,7 +2153,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125113719</v>
+        <v>125113711</v>
       </c>
       <c r="B16" t="n">
         <v>57513</v>
@@ -2203,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454730</v>
+        <v>454543</v>
       </c>
       <c r="R16" t="n">
-        <v>6992234</v>
+        <v>6992277</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2233,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2377,7 +2367,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125113775</v>
+        <v>125113728</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2417,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454618</v>
+        <v>454803</v>
       </c>
       <c r="R18" t="n">
-        <v>6992151</v>
+        <v>6991945</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2484,7 +2474,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125113712</v>
+        <v>125113725</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2524,10 +2514,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454510</v>
+        <v>454746</v>
       </c>
       <c r="R19" t="n">
-        <v>6992297</v>
+        <v>6992129</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,7 +2554,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,7 +2581,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125113705</v>
+        <v>125113703</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2624,17 +2614,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Möckelåsbodarna V, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454690</v>
+        <v>454696</v>
       </c>
       <c r="R20" t="n">
-        <v>6991954</v>
+        <v>6991939</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2667,11 +2677,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,7 +2703,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125113708</v>
+        <v>125113712</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2738,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454646</v>
+        <v>454510</v>
       </c>
       <c r="R21" t="n">
-        <v>6992125</v>
+        <v>6992297</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,7 +2810,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125113717</v>
+        <v>125113724</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -2845,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454766</v>
+        <v>454720</v>
       </c>
       <c r="R22" t="n">
-        <v>6992229</v>
+        <v>6992151</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2912,10 +2917,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125113780</v>
+        <v>125113708</v>
       </c>
       <c r="B23" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2928,21 +2933,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2952,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454741</v>
+        <v>454646</v>
       </c>
       <c r="R23" t="n">
-        <v>6992267</v>
+        <v>6992125</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2988,6 +2993,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,7 +3024,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125113716</v>
+        <v>125113719</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3054,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454781</v>
+        <v>454730</v>
       </c>
       <c r="R24" t="n">
-        <v>6992233</v>
+        <v>6992234</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3121,7 +3131,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125113709</v>
+        <v>125113706</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3161,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454627</v>
+        <v>454605</v>
       </c>
       <c r="R25" t="n">
-        <v>6992167</v>
+        <v>6992025</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3201,7 +3211,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,7 +3238,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125113726</v>
+        <v>125113716</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3268,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454737</v>
+        <v>454781</v>
       </c>
       <c r="R26" t="n">
-        <v>6992033</v>
+        <v>6992233</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3308,7 +3318,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3335,10 +3345,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125113785</v>
+        <v>125113727</v>
       </c>
       <c r="B27" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3351,21 +3361,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3375,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454747</v>
+        <v>454754</v>
       </c>
       <c r="R27" t="n">
-        <v>6992042</v>
+        <v>6992018</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3411,6 +3421,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3437,7 +3452,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125113703</v>
+        <v>125113701</v>
       </c>
       <c r="B28" t="n">
         <v>57513</v>
@@ -3470,37 +3485,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Möckelåsbodarna V, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454696</v>
+        <v>454753</v>
       </c>
       <c r="R28" t="n">
-        <v>6991939</v>
+        <v>6991908</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3533,6 +3528,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 12962-2024 artfynd.xlsx
+++ b/artfynd/A 12962-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113775</v>
+        <v>125113785</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454618</v>
+        <v>454747</v>
       </c>
       <c r="R2" t="n">
-        <v>6992151</v>
+        <v>6992042</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125113778</v>
+        <v>125113725</v>
       </c>
       <c r="B3" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454747</v>
+        <v>454746</v>
       </c>
       <c r="R3" t="n">
-        <v>6992205</v>
+        <v>6992129</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125113717</v>
+        <v>125113712</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454766</v>
+        <v>454510</v>
       </c>
       <c r="R4" t="n">
-        <v>6992229</v>
+        <v>6992297</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113720</v>
+        <v>125113723</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454770</v>
+        <v>454755</v>
       </c>
       <c r="R5" t="n">
-        <v>6992167</v>
+        <v>6992152</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113721</v>
+        <v>125113775</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454767</v>
+        <v>454618</v>
       </c>
       <c r="R6" t="n">
-        <v>6992161</v>
+        <v>6992151</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125113782</v>
+        <v>125113780</v>
       </c>
       <c r="B7" t="n">
         <v>79891</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454747</v>
+        <v>454741</v>
       </c>
       <c r="R7" t="n">
-        <v>6992207</v>
+        <v>6992267</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125113718</v>
+        <v>125113701</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454741</v>
+        <v>454753</v>
       </c>
       <c r="R8" t="n">
-        <v>6992287</v>
+        <v>6991908</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125113722</v>
+        <v>125113718</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454752</v>
+        <v>454741</v>
       </c>
       <c r="R9" t="n">
-        <v>6992152</v>
+        <v>6992287</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125113785</v>
+        <v>125113709</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454747</v>
+        <v>454627</v>
       </c>
       <c r="R10" t="n">
-        <v>6992042</v>
+        <v>6992167</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,6 +1597,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125113707</v>
+        <v>125113711</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1663,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454599</v>
+        <v>454543</v>
       </c>
       <c r="R11" t="n">
-        <v>6992080</v>
+        <v>6992277</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,7 +1708,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113780</v>
+        <v>125113721</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454741</v>
+        <v>454767</v>
       </c>
       <c r="R12" t="n">
-        <v>6992267</v>
+        <v>6992161</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,6 +1811,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113709</v>
+        <v>125113722</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1872,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454627</v>
+        <v>454752</v>
       </c>
       <c r="R13" t="n">
-        <v>6992167</v>
+        <v>6992152</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2046,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125113705</v>
+        <v>125113778</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2062,21 +2072,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454690</v>
+        <v>454747</v>
       </c>
       <c r="R15" t="n">
-        <v>6991954</v>
+        <v>6992205</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,11 +2132,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2153,7 +2158,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125113711</v>
+        <v>125113706</v>
       </c>
       <c r="B16" t="n">
         <v>57513</v>
@@ -2193,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454543</v>
+        <v>454605</v>
       </c>
       <c r="R16" t="n">
-        <v>6992277</v>
+        <v>6992025</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2238,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,7 +2265,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125113723</v>
+        <v>125113703</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2293,17 +2298,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Möckelåsbodarna V, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454755</v>
+        <v>454696</v>
       </c>
       <c r="R17" t="n">
-        <v>6992152</v>
+        <v>6991939</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,11 +2361,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2367,10 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125113728</v>
+        <v>125113782</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,21 +2403,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2407,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454803</v>
+        <v>454747</v>
       </c>
       <c r="R18" t="n">
-        <v>6991945</v>
+        <v>6992207</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2443,11 +2463,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,7 +2489,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125113725</v>
+        <v>125113708</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2514,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454746</v>
+        <v>454646</v>
       </c>
       <c r="R19" t="n">
-        <v>6992129</v>
+        <v>6992125</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2554,7 +2569,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2581,7 +2596,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125113703</v>
+        <v>125113724</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2614,37 +2629,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Möckelåsbodarna V, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454696</v>
+        <v>454720</v>
       </c>
       <c r="R20" t="n">
-        <v>6991939</v>
+        <v>6992151</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2677,6 +2672,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2703,7 +2703,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125113712</v>
+        <v>125113717</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454510</v>
+        <v>454766</v>
       </c>
       <c r="R21" t="n">
-        <v>6992297</v>
+        <v>6992229</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2810,7 +2810,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125113724</v>
+        <v>125113705</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454720</v>
+        <v>454690</v>
       </c>
       <c r="R22" t="n">
-        <v>6992151</v>
+        <v>6991954</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2917,7 +2917,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125113708</v>
+        <v>125113727</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454646</v>
+        <v>454754</v>
       </c>
       <c r="R23" t="n">
-        <v>6992125</v>
+        <v>6992018</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3024,7 +3024,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125113719</v>
+        <v>125113716</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454730</v>
+        <v>454781</v>
       </c>
       <c r="R24" t="n">
-        <v>6992234</v>
+        <v>6992233</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3131,7 +3131,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125113706</v>
+        <v>125113728</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454605</v>
+        <v>454803</v>
       </c>
       <c r="R25" t="n">
-        <v>6992025</v>
+        <v>6991945</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3238,7 +3238,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125113716</v>
+        <v>125113720</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454781</v>
+        <v>454770</v>
       </c>
       <c r="R26" t="n">
-        <v>6992233</v>
+        <v>6992167</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3345,7 +3345,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125113727</v>
+        <v>125113707</v>
       </c>
       <c r="B27" t="n">
         <v>57513</v>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454754</v>
+        <v>454599</v>
       </c>
       <c r="R27" t="n">
-        <v>6992018</v>
+        <v>6992080</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3452,7 +3452,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125113701</v>
+        <v>125113719</v>
       </c>
       <c r="B28" t="n">
         <v>57513</v>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454753</v>
+        <v>454730</v>
       </c>
       <c r="R28" t="n">
-        <v>6991908</v>
+        <v>6992234</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 12962-2024 artfynd.xlsx
+++ b/artfynd/A 12962-2024 artfynd.xlsx
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113723</v>
+        <v>125113780</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454755</v>
+        <v>454741</v>
       </c>
       <c r="R5" t="n">
-        <v>6992152</v>
+        <v>6992267</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113775</v>
+        <v>125113723</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454618</v>
+        <v>454755</v>
       </c>
       <c r="R6" t="n">
-        <v>6992151</v>
+        <v>6992152</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125113780</v>
+        <v>125113775</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454741</v>
+        <v>454618</v>
       </c>
       <c r="R7" t="n">
-        <v>6992267</v>
+        <v>6992151</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1276,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 12962-2024 artfynd.xlsx
+++ b/artfynd/A 12962-2024 artfynd.xlsx
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113780</v>
+        <v>125113723</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454741</v>
+        <v>454755</v>
       </c>
       <c r="R5" t="n">
-        <v>6992267</v>
+        <v>6992152</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113723</v>
+        <v>125113775</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454755</v>
+        <v>454618</v>
       </c>
       <c r="R6" t="n">
-        <v>6992152</v>
+        <v>6992151</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125113775</v>
+        <v>125113780</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454618</v>
+        <v>454741</v>
       </c>
       <c r="R7" t="n">
-        <v>6992151</v>
+        <v>6992267</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,11 +1281,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125113701</v>
+        <v>125113718</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454753</v>
+        <v>454741</v>
       </c>
       <c r="R8" t="n">
-        <v>6991908</v>
+        <v>6992287</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125113718</v>
+        <v>125113701</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454741</v>
+        <v>454753</v>
       </c>
       <c r="R9" t="n">
-        <v>6992287</v>
+        <v>6991908</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 12962-2024 artfynd.xlsx
+++ b/artfynd/A 12962-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113785</v>
+        <v>125113780</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454747</v>
+        <v>454741</v>
       </c>
       <c r="R2" t="n">
-        <v>6992042</v>
+        <v>6992267</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125113725</v>
+        <v>125113722</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454746</v>
+        <v>454752</v>
       </c>
       <c r="R3" t="n">
-        <v>6992129</v>
+        <v>6992152</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125113712</v>
+        <v>125113721</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454510</v>
+        <v>454767</v>
       </c>
       <c r="R4" t="n">
-        <v>6992297</v>
+        <v>6992161</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1098,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113775</v>
+        <v>125113712</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454618</v>
+        <v>454510</v>
       </c>
       <c r="R6" t="n">
-        <v>6992151</v>
+        <v>6992297</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125113780</v>
+        <v>125113711</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454741</v>
+        <v>454543</v>
       </c>
       <c r="R7" t="n">
-        <v>6992267</v>
+        <v>6992277</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125113718</v>
+        <v>125113782</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454741</v>
+        <v>454747</v>
       </c>
       <c r="R8" t="n">
-        <v>6992287</v>
+        <v>6992207</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,11 +1388,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125113701</v>
+        <v>125113778</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454753</v>
+        <v>454747</v>
       </c>
       <c r="R9" t="n">
-        <v>6991908</v>
+        <v>6992205</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,11 +1490,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125113709</v>
+        <v>125113708</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1561,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454627</v>
+        <v>454646</v>
       </c>
       <c r="R10" t="n">
-        <v>6992167</v>
+        <v>6992125</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1596,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,7 +1623,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125113711</v>
+        <v>125113706</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1668,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454543</v>
+        <v>454605</v>
       </c>
       <c r="R11" t="n">
-        <v>6992277</v>
+        <v>6992025</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1703,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1730,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113721</v>
+        <v>125113701</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1775,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454767</v>
+        <v>454753</v>
       </c>
       <c r="R12" t="n">
-        <v>6992161</v>
+        <v>6991908</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,7 +1837,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113722</v>
+        <v>125113707</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1882,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454752</v>
+        <v>454599</v>
       </c>
       <c r="R13" t="n">
-        <v>6992152</v>
+        <v>6992080</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1949,7 +1944,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113726</v>
+        <v>125113703</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -1982,17 +1977,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Möckelåsbodarna V, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454737</v>
+        <v>454696</v>
       </c>
       <c r="R14" t="n">
-        <v>6992033</v>
+        <v>6991939</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,11 +2040,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125113778</v>
+        <v>125113705</v>
       </c>
       <c r="B15" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2072,21 +2082,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454747</v>
+        <v>454690</v>
       </c>
       <c r="R15" t="n">
-        <v>6992205</v>
+        <v>6991954</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,6 +2142,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,10 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125113706</v>
+        <v>125113785</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2174,21 +2189,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454605</v>
+        <v>454747</v>
       </c>
       <c r="R16" t="n">
-        <v>6992025</v>
+        <v>6992042</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,11 +2249,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2265,7 +2275,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125113703</v>
+        <v>125113719</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2298,37 +2308,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Möckelåsbodarna V, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454696</v>
+        <v>454730</v>
       </c>
       <c r="R17" t="n">
-        <v>6991939</v>
+        <v>6992234</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2361,6 +2351,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,10 +2382,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125113782</v>
+        <v>125113775</v>
       </c>
       <c r="B18" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2403,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2427,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454747</v>
+        <v>454618</v>
       </c>
       <c r="R18" t="n">
-        <v>6992207</v>
+        <v>6992151</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2463,6 +2458,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,7 +2489,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125113708</v>
+        <v>125113720</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454646</v>
+        <v>454770</v>
       </c>
       <c r="R19" t="n">
-        <v>6992125</v>
+        <v>6992167</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2596,7 +2596,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125113724</v>
+        <v>125113725</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454720</v>
+        <v>454746</v>
       </c>
       <c r="R20" t="n">
-        <v>6992151</v>
+        <v>6992129</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2810,7 +2810,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125113705</v>
+        <v>125113718</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -2850,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454690</v>
+        <v>454741</v>
       </c>
       <c r="R22" t="n">
-        <v>6991954</v>
+        <v>6992287</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2917,7 +2917,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125113727</v>
+        <v>125113728</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454754</v>
+        <v>454803</v>
       </c>
       <c r="R23" t="n">
-        <v>6992018</v>
+        <v>6991945</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3024,7 +3024,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125113716</v>
+        <v>125113727</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454781</v>
+        <v>454754</v>
       </c>
       <c r="R24" t="n">
-        <v>6992233</v>
+        <v>6992018</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3131,7 +3131,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125113728</v>
+        <v>125113726</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454803</v>
+        <v>454737</v>
       </c>
       <c r="R25" t="n">
-        <v>6991945</v>
+        <v>6992033</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3238,7 +3238,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125113720</v>
+        <v>125113716</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454770</v>
+        <v>454781</v>
       </c>
       <c r="R26" t="n">
-        <v>6992167</v>
+        <v>6992233</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3345,7 +3345,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125113707</v>
+        <v>125113709</v>
       </c>
       <c r="B27" t="n">
         <v>57513</v>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454599</v>
+        <v>454627</v>
       </c>
       <c r="R27" t="n">
-        <v>6992080</v>
+        <v>6992167</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3452,7 +3452,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125113719</v>
+        <v>125113724</v>
       </c>
       <c r="B28" t="n">
         <v>57513</v>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454730</v>
+        <v>454720</v>
       </c>
       <c r="R28" t="n">
-        <v>6992234</v>
+        <v>6992151</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 12962-2024 artfynd.xlsx
+++ b/artfynd/A 12962-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113780</v>
+        <v>125113726</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454741</v>
+        <v>454737</v>
       </c>
       <c r="R2" t="n">
-        <v>6992267</v>
+        <v>6992033</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125113722</v>
+        <v>125113712</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454752</v>
+        <v>454510</v>
       </c>
       <c r="R3" t="n">
-        <v>6992152</v>
+        <v>6992297</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125113721</v>
+        <v>125113709</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454767</v>
+        <v>454627</v>
       </c>
       <c r="R4" t="n">
-        <v>6992161</v>
+        <v>6992167</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113723</v>
+        <v>125113718</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454755</v>
+        <v>454741</v>
       </c>
       <c r="R5" t="n">
-        <v>6992152</v>
+        <v>6992287</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113712</v>
+        <v>125113723</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454510</v>
+        <v>454755</v>
       </c>
       <c r="R6" t="n">
-        <v>6992297</v>
+        <v>6992152</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125113711</v>
+        <v>125113717</v>
       </c>
       <c r="B7" t="n">
         <v>57513</v>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454543</v>
+        <v>454766</v>
       </c>
       <c r="R7" t="n">
-        <v>6992277</v>
+        <v>6992229</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125113778</v>
+        <v>125113785</v>
       </c>
       <c r="B9" t="n">
-        <v>79892</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,7 +1462,7 @@
         <v>454747</v>
       </c>
       <c r="R9" t="n">
-        <v>6992205</v>
+        <v>6992042</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125113708</v>
+        <v>125113722</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1556,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454646</v>
+        <v>454752</v>
       </c>
       <c r="R10" t="n">
-        <v>6992125</v>
+        <v>6992152</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125113706</v>
+        <v>125113705</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1663,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454605</v>
+        <v>454690</v>
       </c>
       <c r="R11" t="n">
-        <v>6992025</v>
+        <v>6991954</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,7 +1708,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113701</v>
+        <v>125113775</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1770,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454753</v>
+        <v>454618</v>
       </c>
       <c r="R12" t="n">
-        <v>6991908</v>
+        <v>6992151</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113707</v>
+        <v>125113701</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1877,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454599</v>
+        <v>454753</v>
       </c>
       <c r="R13" t="n">
-        <v>6992080</v>
+        <v>6991908</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,7 +1949,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113703</v>
+        <v>125113725</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -1977,37 +1982,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Möckelåsbodarna V, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454696</v>
+        <v>454746</v>
       </c>
       <c r="R14" t="n">
-        <v>6991939</v>
+        <v>6992129</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2040,6 +2025,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2066,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125113705</v>
+        <v>125113727</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2106,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454690</v>
+        <v>454754</v>
       </c>
       <c r="R15" t="n">
-        <v>6991954</v>
+        <v>6992018</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2136,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2173,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125113785</v>
+        <v>125113703</v>
       </c>
       <c r="B16" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2189,34 +2179,54 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Möckelåsbodarna V, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454747</v>
+        <v>454696</v>
       </c>
       <c r="R16" t="n">
-        <v>6992042</v>
+        <v>6991939</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2275,7 +2285,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125113719</v>
+        <v>125113728</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2315,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454730</v>
+        <v>454803</v>
       </c>
       <c r="R17" t="n">
-        <v>6992234</v>
+        <v>6991945</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,7 +2365,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2382,7 +2392,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125113775</v>
+        <v>125113719</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2422,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454618</v>
+        <v>454730</v>
       </c>
       <c r="R18" t="n">
-        <v>6992151</v>
+        <v>6992234</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,7 +2472,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2489,7 +2499,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125113720</v>
+        <v>125113708</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2529,10 +2539,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454770</v>
+        <v>454646</v>
       </c>
       <c r="R19" t="n">
-        <v>6992167</v>
+        <v>6992125</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2569,7 +2579,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2596,7 +2606,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125113725</v>
+        <v>125113720</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2636,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454746</v>
+        <v>454770</v>
       </c>
       <c r="R20" t="n">
-        <v>6992129</v>
+        <v>6992167</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2676,7 +2686,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2703,7 +2713,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125113717</v>
+        <v>125113721</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2743,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454766</v>
+        <v>454767</v>
       </c>
       <c r="R21" t="n">
-        <v>6992229</v>
+        <v>6992161</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2810,7 +2820,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125113718</v>
+        <v>125113707</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -2850,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454741</v>
+        <v>454599</v>
       </c>
       <c r="R22" t="n">
-        <v>6992287</v>
+        <v>6992080</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2917,10 +2927,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125113728</v>
+        <v>125113780</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2933,21 +2943,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2957,10 +2967,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454803</v>
+        <v>454741</v>
       </c>
       <c r="R23" t="n">
-        <v>6991945</v>
+        <v>6992267</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2993,11 +3003,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3024,7 +3029,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125113727</v>
+        <v>125113711</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3064,10 +3069,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454754</v>
+        <v>454543</v>
       </c>
       <c r="R24" t="n">
-        <v>6992018</v>
+        <v>6992277</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3104,7 +3109,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3131,7 +3136,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125113726</v>
+        <v>125113706</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3171,10 +3176,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454737</v>
+        <v>454605</v>
       </c>
       <c r="R25" t="n">
-        <v>6992033</v>
+        <v>6992025</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3211,7 +3216,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3345,10 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125113709</v>
+        <v>125113778</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3361,21 +3366,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3385,10 +3390,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454627</v>
+        <v>454747</v>
       </c>
       <c r="R27" t="n">
-        <v>6992167</v>
+        <v>6992205</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3421,11 +3426,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 12962-2024 artfynd.xlsx
+++ b/artfynd/A 12962-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113726</v>
+        <v>125113722</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454737</v>
+        <v>454752</v>
       </c>
       <c r="R2" t="n">
-        <v>6992033</v>
+        <v>6992152</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125113712</v>
+        <v>125113705</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454510</v>
+        <v>454690</v>
       </c>
       <c r="R3" t="n">
-        <v>6992297</v>
+        <v>6991954</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125113709</v>
+        <v>125113728</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454627</v>
+        <v>454803</v>
       </c>
       <c r="R4" t="n">
-        <v>6992167</v>
+        <v>6991945</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113718</v>
+        <v>125113727</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454741</v>
+        <v>454754</v>
       </c>
       <c r="R5" t="n">
-        <v>6992287</v>
+        <v>6992018</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113723</v>
+        <v>125113703</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1136,17 +1136,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Möckelåsbodarna V, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454755</v>
+        <v>454696</v>
       </c>
       <c r="R6" t="n">
-        <v>6992152</v>
+        <v>6991939</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,11 +1199,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125113717</v>
+        <v>125113778</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454766</v>
+        <v>454747</v>
       </c>
       <c r="R7" t="n">
-        <v>6992229</v>
+        <v>6992205</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,11 +1301,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125113782</v>
+        <v>125113785</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>91030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1360,7 +1370,7 @@
         <v>454747</v>
       </c>
       <c r="R8" t="n">
-        <v>6992207</v>
+        <v>6992042</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1419,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125113785</v>
+        <v>125113720</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,21 +1445,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454747</v>
+        <v>454770</v>
       </c>
       <c r="R9" t="n">
-        <v>6992042</v>
+        <v>6992167</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,6 +1505,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125113722</v>
+        <v>125113724</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1561,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454752</v>
+        <v>454720</v>
       </c>
       <c r="R10" t="n">
-        <v>6992152</v>
+        <v>6992151</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1628,7 +1643,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125113705</v>
+        <v>125113719</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1668,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454690</v>
+        <v>454730</v>
       </c>
       <c r="R11" t="n">
-        <v>6991954</v>
+        <v>6992234</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1723,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1750,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113775</v>
+        <v>125113721</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1775,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454618</v>
+        <v>454767</v>
       </c>
       <c r="R12" t="n">
-        <v>6992151</v>
+        <v>6992161</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,7 +1857,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113701</v>
+        <v>125113707</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1882,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454753</v>
+        <v>454599</v>
       </c>
       <c r="R13" t="n">
-        <v>6991908</v>
+        <v>6992080</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1949,7 +1964,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113725</v>
+        <v>125113709</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -1989,10 +2004,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454746</v>
+        <v>454627</v>
       </c>
       <c r="R14" t="n">
-        <v>6992129</v>
+        <v>6992167</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2029,7 +2044,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,7 +2071,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125113727</v>
+        <v>125113712</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2096,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454754</v>
+        <v>454510</v>
       </c>
       <c r="R15" t="n">
-        <v>6992018</v>
+        <v>6992297</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2136,7 +2151,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,10 +2178,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125113703</v>
+        <v>125113782</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2179,54 +2194,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Möckelåsbodarna V, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454696</v>
+        <v>454747</v>
       </c>
       <c r="R16" t="n">
-        <v>6991939</v>
+        <v>6992207</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2285,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125113728</v>
+        <v>125113708</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2325,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454803</v>
+        <v>454646</v>
       </c>
       <c r="R17" t="n">
-        <v>6991945</v>
+        <v>6992125</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2360,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2392,7 +2387,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125113719</v>
+        <v>125113718</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2432,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454730</v>
+        <v>454741</v>
       </c>
       <c r="R18" t="n">
-        <v>6992234</v>
+        <v>6992287</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2472,7 +2467,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2499,7 +2494,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125113708</v>
+        <v>125113717</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2539,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454646</v>
+        <v>454766</v>
       </c>
       <c r="R19" t="n">
-        <v>6992125</v>
+        <v>6992229</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,7 +2574,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2606,7 +2601,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125113720</v>
+        <v>125113775</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2646,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454770</v>
+        <v>454618</v>
       </c>
       <c r="R20" t="n">
-        <v>6992167</v>
+        <v>6992151</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2713,7 +2708,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125113721</v>
+        <v>125113701</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2753,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454767</v>
+        <v>454753</v>
       </c>
       <c r="R21" t="n">
-        <v>6992161</v>
+        <v>6991908</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2820,7 +2815,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125113707</v>
+        <v>125113716</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -2860,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454599</v>
+        <v>454781</v>
       </c>
       <c r="R22" t="n">
-        <v>6992080</v>
+        <v>6992233</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2900,7 +2895,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3136,7 +3131,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125113706</v>
+        <v>125113725</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3176,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454605</v>
+        <v>454746</v>
       </c>
       <c r="R25" t="n">
-        <v>6992025</v>
+        <v>6992129</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3216,7 +3211,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,7 +3238,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125113716</v>
+        <v>125113726</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3283,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454781</v>
+        <v>454737</v>
       </c>
       <c r="R26" t="n">
-        <v>6992233</v>
+        <v>6992033</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3323,7 +3318,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,10 +3345,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125113778</v>
+        <v>125113706</v>
       </c>
       <c r="B27" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3366,21 +3361,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3390,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454747</v>
+        <v>454605</v>
       </c>
       <c r="R27" t="n">
-        <v>6992205</v>
+        <v>6992025</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3426,6 +3421,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3452,7 +3452,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125113724</v>
+        <v>125113723</v>
       </c>
       <c r="B28" t="n">
         <v>57513</v>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454720</v>
+        <v>454755</v>
       </c>
       <c r="R28" t="n">
-        <v>6992151</v>
+        <v>6992152</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 12962-2024 artfynd.xlsx
+++ b/artfynd/A 12962-2024 artfynd.xlsx
@@ -1643,7 +1643,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125113719</v>
+        <v>125113721</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454730</v>
+        <v>454767</v>
       </c>
       <c r="R11" t="n">
-        <v>6992234</v>
+        <v>6992161</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1750,7 +1750,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113721</v>
+        <v>125113719</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454767</v>
+        <v>454730</v>
       </c>
       <c r="R12" t="n">
-        <v>6992161</v>
+        <v>6992234</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2494,7 +2494,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125113717</v>
+        <v>125113775</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454766</v>
+        <v>454618</v>
       </c>
       <c r="R19" t="n">
-        <v>6992229</v>
+        <v>6992151</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2601,7 +2601,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125113775</v>
+        <v>125113717</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2641,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454618</v>
+        <v>454766</v>
       </c>
       <c r="R20" t="n">
-        <v>6992151</v>
+        <v>6992229</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 12962-2024 artfynd.xlsx
+++ b/artfynd/A 12962-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113722</v>
+        <v>125113719</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454752</v>
+        <v>454730</v>
       </c>
       <c r="R2" t="n">
-        <v>6992152</v>
+        <v>6992234</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125113705</v>
+        <v>125113728</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454690</v>
+        <v>454803</v>
       </c>
       <c r="R3" t="n">
-        <v>6991954</v>
+        <v>6991945</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125113728</v>
+        <v>125113709</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454803</v>
+        <v>454627</v>
       </c>
       <c r="R4" t="n">
-        <v>6991945</v>
+        <v>6992167</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113727</v>
+        <v>125113780</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454754</v>
+        <v>454741</v>
       </c>
       <c r="R5" t="n">
-        <v>6992018</v>
+        <v>6992267</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113703</v>
+        <v>125113707</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1136,37 +1131,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Möckelåsbodarna V, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454696</v>
+        <v>454599</v>
       </c>
       <c r="R6" t="n">
-        <v>6991939</v>
+        <v>6992080</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125113778</v>
+        <v>125113785</v>
       </c>
       <c r="B7" t="n">
-        <v>79892</v>
+        <v>91030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1268,7 +1248,7 @@
         <v>454747</v>
       </c>
       <c r="R7" t="n">
-        <v>6992205</v>
+        <v>6992042</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125113785</v>
+        <v>125113701</v>
       </c>
       <c r="B8" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1367,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454747</v>
+        <v>454753</v>
       </c>
       <c r="R8" t="n">
-        <v>6992042</v>
+        <v>6991908</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,6 +1383,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125113720</v>
+        <v>125113725</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1469,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454770</v>
+        <v>454746</v>
       </c>
       <c r="R9" t="n">
-        <v>6992167</v>
+        <v>6992129</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125113724</v>
+        <v>125113718</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1576,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454720</v>
+        <v>454741</v>
       </c>
       <c r="R10" t="n">
-        <v>6992151</v>
+        <v>6992287</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125113721</v>
+        <v>125113782</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454767</v>
+        <v>454747</v>
       </c>
       <c r="R11" t="n">
-        <v>6992161</v>
+        <v>6992207</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,11 +1704,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1750,7 +1730,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113719</v>
+        <v>125113726</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1790,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454730</v>
+        <v>454737</v>
       </c>
       <c r="R12" t="n">
-        <v>6992234</v>
+        <v>6992033</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1830,7 +1810,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1857,7 +1837,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113707</v>
+        <v>125113724</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1897,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454599</v>
+        <v>454720</v>
       </c>
       <c r="R13" t="n">
-        <v>6992080</v>
+        <v>6992151</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1964,7 +1944,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113709</v>
+        <v>125113775</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -2004,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454627</v>
+        <v>454618</v>
       </c>
       <c r="R14" t="n">
-        <v>6992167</v>
+        <v>6992151</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2071,7 +2051,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125113712</v>
+        <v>125113721</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2111,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454510</v>
+        <v>454767</v>
       </c>
       <c r="R15" t="n">
-        <v>6992297</v>
+        <v>6992161</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,7 +2131,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2178,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125113782</v>
+        <v>125113720</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2194,21 +2174,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454747</v>
+        <v>454770</v>
       </c>
       <c r="R16" t="n">
-        <v>6992207</v>
+        <v>6992167</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,6 +2234,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2280,10 +2265,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125113708</v>
+        <v>125113778</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2296,21 +2281,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2320,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454646</v>
+        <v>454747</v>
       </c>
       <c r="R17" t="n">
-        <v>6992125</v>
+        <v>6992205</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2356,11 +2341,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2387,7 +2367,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125113718</v>
+        <v>125113716</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2427,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454741</v>
+        <v>454781</v>
       </c>
       <c r="R18" t="n">
-        <v>6992287</v>
+        <v>6992233</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2467,7 +2447,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2494,7 +2474,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125113775</v>
+        <v>125113712</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2534,10 +2514,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454618</v>
+        <v>454510</v>
       </c>
       <c r="R19" t="n">
-        <v>6992151</v>
+        <v>6992297</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,7 +2554,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2601,7 +2581,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125113717</v>
+        <v>125113711</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2641,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454766</v>
+        <v>454543</v>
       </c>
       <c r="R20" t="n">
-        <v>6992229</v>
+        <v>6992277</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2681,7 +2661,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,7 +2688,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125113701</v>
+        <v>125113708</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2748,10 +2728,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454753</v>
+        <v>454646</v>
       </c>
       <c r="R21" t="n">
-        <v>6991908</v>
+        <v>6992125</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2788,7 +2768,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,7 +2795,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125113716</v>
+        <v>125113703</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -2848,17 +2828,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Möckelåsbodarna V, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454781</v>
+        <v>454696</v>
       </c>
       <c r="R22" t="n">
-        <v>6992233</v>
+        <v>6991939</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2891,11 +2891,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,10 +2917,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125113780</v>
+        <v>125113727</v>
       </c>
       <c r="B23" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2938,21 +2933,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2962,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454741</v>
+        <v>454754</v>
       </c>
       <c r="R23" t="n">
-        <v>6992267</v>
+        <v>6992018</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2998,6 +2993,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3024,7 +3024,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125113711</v>
+        <v>125113723</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454543</v>
+        <v>454755</v>
       </c>
       <c r="R24" t="n">
-        <v>6992277</v>
+        <v>6992152</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3131,7 +3131,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125113725</v>
+        <v>125113705</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454746</v>
+        <v>454690</v>
       </c>
       <c r="R25" t="n">
-        <v>6992129</v>
+        <v>6991954</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3238,7 +3238,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125113726</v>
+        <v>125113717</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454737</v>
+        <v>454766</v>
       </c>
       <c r="R26" t="n">
-        <v>6992033</v>
+        <v>6992229</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3345,7 +3345,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125113706</v>
+        <v>125113722</v>
       </c>
       <c r="B27" t="n">
         <v>57513</v>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454605</v>
+        <v>454752</v>
       </c>
       <c r="R27" t="n">
-        <v>6992025</v>
+        <v>6992152</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3452,7 +3452,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125113723</v>
+        <v>125113706</v>
       </c>
       <c r="B28" t="n">
         <v>57513</v>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454755</v>
+        <v>454605</v>
       </c>
       <c r="R28" t="n">
-        <v>6992152</v>
+        <v>6992025</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 12962-2024 artfynd.xlsx
+++ b/artfynd/A 12962-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113719</v>
+        <v>125113718</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454730</v>
+        <v>454741</v>
       </c>
       <c r="R2" t="n">
-        <v>6992234</v>
+        <v>6992287</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125113728</v>
+        <v>125113778</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454803</v>
+        <v>454747</v>
       </c>
       <c r="R3" t="n">
-        <v>6991945</v>
+        <v>6992205</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125113709</v>
+        <v>125113701</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454627</v>
+        <v>454753</v>
       </c>
       <c r="R4" t="n">
-        <v>6992167</v>
+        <v>6991908</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113780</v>
+        <v>125113703</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,34 +1007,54 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Möckelåsbodarna V, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454741</v>
+        <v>454696</v>
       </c>
       <c r="R5" t="n">
-        <v>6992267</v>
+        <v>6991939</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113707</v>
+        <v>125113709</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1138,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454599</v>
+        <v>454627</v>
       </c>
       <c r="R6" t="n">
-        <v>6992080</v>
+        <v>6992167</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125113785</v>
+        <v>125113707</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1236,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454747</v>
+        <v>454599</v>
       </c>
       <c r="R7" t="n">
-        <v>6992042</v>
+        <v>6992080</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1296,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125113701</v>
+        <v>125113780</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454753</v>
+        <v>454741</v>
       </c>
       <c r="R8" t="n">
-        <v>6991908</v>
+        <v>6992267</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,11 +1403,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,7 +1429,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125113725</v>
+        <v>125113775</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1454,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454746</v>
+        <v>454618</v>
       </c>
       <c r="R9" t="n">
-        <v>6992129</v>
+        <v>6992151</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1509,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125113718</v>
+        <v>125113785</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,21 +1552,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454741</v>
+        <v>454747</v>
       </c>
       <c r="R10" t="n">
-        <v>6992287</v>
+        <v>6992042</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,11 +1612,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125113782</v>
+        <v>125113719</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1654,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454747</v>
+        <v>454730</v>
       </c>
       <c r="R11" t="n">
-        <v>6992207</v>
+        <v>6992234</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,6 +1714,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113726</v>
+        <v>125113725</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1770,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454737</v>
+        <v>454746</v>
       </c>
       <c r="R12" t="n">
-        <v>6992033</v>
+        <v>6992129</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,7 +1825,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113775</v>
+        <v>125113782</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,21 +1975,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454618</v>
+        <v>454747</v>
       </c>
       <c r="R14" t="n">
-        <v>6992151</v>
+        <v>6992207</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,11 +2035,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2051,7 +2061,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125113721</v>
+        <v>125113705</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2091,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454767</v>
+        <v>454690</v>
       </c>
       <c r="R15" t="n">
-        <v>6992161</v>
+        <v>6991954</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2131,7 +2141,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,7 +2168,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125113720</v>
+        <v>125113726</v>
       </c>
       <c r="B16" t="n">
         <v>57513</v>
@@ -2198,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454770</v>
+        <v>454737</v>
       </c>
       <c r="R16" t="n">
-        <v>6992167</v>
+        <v>6992033</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125113778</v>
+        <v>125113720</v>
       </c>
       <c r="B17" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2281,21 +2291,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454747</v>
+        <v>454770</v>
       </c>
       <c r="R17" t="n">
-        <v>6992205</v>
+        <v>6992167</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2341,6 +2351,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2367,7 +2382,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125113716</v>
+        <v>125113721</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2407,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454781</v>
+        <v>454767</v>
       </c>
       <c r="R18" t="n">
-        <v>6992233</v>
+        <v>6992161</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,7 +2462,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,7 +2489,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125113712</v>
+        <v>125113723</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2514,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454510</v>
+        <v>454755</v>
       </c>
       <c r="R19" t="n">
-        <v>6992297</v>
+        <v>6992152</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2554,7 +2569,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2581,7 +2596,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125113711</v>
+        <v>125113712</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2621,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454543</v>
+        <v>454510</v>
       </c>
       <c r="R20" t="n">
-        <v>6992277</v>
+        <v>6992297</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2661,7 +2676,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2688,7 +2703,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125113708</v>
+        <v>125113728</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2728,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454646</v>
+        <v>454803</v>
       </c>
       <c r="R21" t="n">
-        <v>6992125</v>
+        <v>6991945</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2768,7 +2783,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2795,7 +2810,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125113703</v>
+        <v>125113717</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -2828,37 +2843,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Möckelåsbodarna V, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454696</v>
+        <v>454766</v>
       </c>
       <c r="R22" t="n">
-        <v>6991939</v>
+        <v>6992229</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2891,6 +2886,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2917,7 +2917,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125113727</v>
+        <v>125113706</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454754</v>
+        <v>454605</v>
       </c>
       <c r="R23" t="n">
-        <v>6992018</v>
+        <v>6992025</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3024,7 +3024,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125113723</v>
+        <v>125113722</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454755</v>
+        <v>454752</v>
       </c>
       <c r="R24" t="n">
         <v>6992152</v>
@@ -3131,7 +3131,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125113705</v>
+        <v>125113716</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454690</v>
+        <v>454781</v>
       </c>
       <c r="R25" t="n">
-        <v>6991954</v>
+        <v>6992233</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3238,7 +3238,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125113717</v>
+        <v>125113708</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454766</v>
+        <v>454646</v>
       </c>
       <c r="R26" t="n">
-        <v>6992229</v>
+        <v>6992125</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3345,7 +3345,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125113722</v>
+        <v>125113727</v>
       </c>
       <c r="B27" t="n">
         <v>57513</v>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454752</v>
+        <v>454754</v>
       </c>
       <c r="R27" t="n">
-        <v>6992152</v>
+        <v>6992018</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3452,7 +3452,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125113706</v>
+        <v>125113711</v>
       </c>
       <c r="B28" t="n">
         <v>57513</v>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454605</v>
+        <v>454543</v>
       </c>
       <c r="R28" t="n">
-        <v>6992025</v>
+        <v>6992277</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 12962-2024 artfynd.xlsx
+++ b/artfynd/A 12962-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113718</v>
+        <v>125113725</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454741</v>
+        <v>454746</v>
       </c>
       <c r="R2" t="n">
-        <v>6992287</v>
+        <v>6992129</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125113778</v>
+        <v>125113708</v>
       </c>
       <c r="B3" t="n">
-        <v>79892</v>
+        <v>57635</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454747</v>
+        <v>454646</v>
       </c>
       <c r="R3" t="n">
-        <v>6992205</v>
+        <v>6992125</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,7 +892,7 @@
         <v>125113701</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113703</v>
+        <v>125113705</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,37 +1029,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Möckelåsbodarna V, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454696</v>
+        <v>454690</v>
       </c>
       <c r="R5" t="n">
-        <v>6991939</v>
+        <v>6991954</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113709</v>
+        <v>125113724</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454627</v>
+        <v>454720</v>
       </c>
       <c r="R6" t="n">
-        <v>6992167</v>
+        <v>6992151</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125113707</v>
+        <v>125113727</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454599</v>
+        <v>454754</v>
       </c>
       <c r="R7" t="n">
-        <v>6992080</v>
+        <v>6992018</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125113780</v>
+        <v>125113717</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1367,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454741</v>
+        <v>454766</v>
       </c>
       <c r="R8" t="n">
-        <v>6992267</v>
+        <v>6992229</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,6 +1393,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125113775</v>
+        <v>125113711</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1469,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454618</v>
+        <v>454543</v>
       </c>
       <c r="R9" t="n">
-        <v>6992151</v>
+        <v>6992277</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,7 +1504,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125113785</v>
+        <v>125113775</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>57635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1552,21 +1547,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1571,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454747</v>
+        <v>454618</v>
       </c>
       <c r="R10" t="n">
-        <v>6992042</v>
+        <v>6992151</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,6 +1607,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125113719</v>
+        <v>125113720</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454730</v>
+        <v>454770</v>
       </c>
       <c r="R11" t="n">
-        <v>6992234</v>
+        <v>6992167</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113725</v>
+        <v>125113718</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454746</v>
+        <v>454741</v>
       </c>
       <c r="R12" t="n">
-        <v>6992129</v>
+        <v>6992287</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113724</v>
+        <v>125113707</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454720</v>
+        <v>454599</v>
       </c>
       <c r="R13" t="n">
-        <v>6992151</v>
+        <v>6992080</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113782</v>
+        <v>125113703</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1975,34 +1975,54 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Möckelåsbodarna V, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454747</v>
+        <v>454696</v>
       </c>
       <c r="R14" t="n">
-        <v>6992207</v>
+        <v>6991939</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2061,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125113705</v>
+        <v>125113780</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>80028</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2077,21 +2097,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,10 +2121,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454690</v>
+        <v>454741</v>
       </c>
       <c r="R15" t="n">
-        <v>6991954</v>
+        <v>6992267</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2137,11 +2157,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2168,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125113726</v>
+        <v>125113709</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2208,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454737</v>
+        <v>454627</v>
       </c>
       <c r="R16" t="n">
-        <v>6992033</v>
+        <v>6992167</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2275,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125113720</v>
+        <v>125113728</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2315,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454770</v>
+        <v>454803</v>
       </c>
       <c r="R17" t="n">
-        <v>6992167</v>
+        <v>6991945</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2382,10 +2397,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125113721</v>
+        <v>125113723</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2422,10 +2437,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454767</v>
+        <v>454755</v>
       </c>
       <c r="R18" t="n">
-        <v>6992161</v>
+        <v>6992152</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2489,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125113723</v>
+        <v>125113778</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>80029</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2505,21 +2520,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454755</v>
+        <v>454747</v>
       </c>
       <c r="R19" t="n">
-        <v>6992152</v>
+        <v>6992205</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2565,11 +2580,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2596,10 +2606,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125113712</v>
+        <v>125113716</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2636,10 +2646,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454510</v>
+        <v>454781</v>
       </c>
       <c r="R20" t="n">
-        <v>6992297</v>
+        <v>6992233</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2676,7 +2686,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2703,10 +2713,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125113728</v>
+        <v>125113721</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2743,10 +2753,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454803</v>
+        <v>454767</v>
       </c>
       <c r="R21" t="n">
-        <v>6991945</v>
+        <v>6992161</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2810,10 +2820,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125113717</v>
+        <v>125113785</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>91184</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2826,21 +2836,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2860,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454766</v>
+        <v>454747</v>
       </c>
       <c r="R22" t="n">
-        <v>6992229</v>
+        <v>6992042</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2886,11 +2896,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2917,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125113706</v>
+        <v>125113722</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2957,10 +2962,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454605</v>
+        <v>454752</v>
       </c>
       <c r="R23" t="n">
-        <v>6992025</v>
+        <v>6992152</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2997,7 +3002,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3024,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125113722</v>
+        <v>125113782</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>80028</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3040,21 +3045,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,10 +3069,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454752</v>
+        <v>454747</v>
       </c>
       <c r="R24" t="n">
-        <v>6992152</v>
+        <v>6992207</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3100,11 +3105,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3131,10 +3131,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125113716</v>
+        <v>125113712</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454781</v>
+        <v>454510</v>
       </c>
       <c r="R25" t="n">
-        <v>6992233</v>
+        <v>6992297</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3238,10 +3238,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125113708</v>
+        <v>125113719</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454646</v>
+        <v>454730</v>
       </c>
       <c r="R26" t="n">
-        <v>6992125</v>
+        <v>6992234</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3345,10 +3345,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125113727</v>
+        <v>125113726</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454754</v>
+        <v>454737</v>
       </c>
       <c r="R27" t="n">
-        <v>6992018</v>
+        <v>6992033</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3452,10 +3452,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125113711</v>
+        <v>125113706</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3492,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454543</v>
+        <v>454605</v>
       </c>
       <c r="R28" t="n">
-        <v>6992277</v>
+        <v>6992025</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 12962-2024 artfynd.xlsx
+++ b/artfynd/A 12962-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113725</v>
+        <v>125113780</v>
       </c>
       <c r="B2" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454746</v>
+        <v>454741</v>
       </c>
       <c r="R2" t="n">
-        <v>6992129</v>
+        <v>6992267</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125113708</v>
+        <v>125113778</v>
       </c>
       <c r="B3" t="n">
-        <v>57635</v>
+        <v>80029</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454646</v>
+        <v>454747</v>
       </c>
       <c r="R3" t="n">
-        <v>6992125</v>
+        <v>6992205</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125113701</v>
+        <v>125113728</v>
       </c>
       <c r="B4" t="n">
         <v>57635</v>
@@ -929,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454753</v>
+        <v>454803</v>
       </c>
       <c r="R4" t="n">
-        <v>6991908</v>
+        <v>6991945</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113705</v>
+        <v>125113707</v>
       </c>
       <c r="B5" t="n">
         <v>57635</v>
@@ -1036,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454690</v>
+        <v>454599</v>
       </c>
       <c r="R5" t="n">
-        <v>6991954</v>
+        <v>6992080</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1066,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113724</v>
+        <v>125113723</v>
       </c>
       <c r="B6" t="n">
         <v>57635</v>
@@ -1143,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454720</v>
+        <v>454755</v>
       </c>
       <c r="R6" t="n">
-        <v>6992151</v>
+        <v>6992152</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125113727</v>
+        <v>125113711</v>
       </c>
       <c r="B7" t="n">
         <v>57635</v>
@@ -1250,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454754</v>
+        <v>454543</v>
       </c>
       <c r="R7" t="n">
-        <v>6992018</v>
+        <v>6992277</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125113717</v>
+        <v>125113705</v>
       </c>
       <c r="B8" t="n">
         <v>57635</v>
@@ -1357,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454766</v>
+        <v>454690</v>
       </c>
       <c r="R8" t="n">
-        <v>6992229</v>
+        <v>6991954</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1387,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,7 +1414,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125113711</v>
+        <v>125113718</v>
       </c>
       <c r="B9" t="n">
         <v>57635</v>
@@ -1464,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454543</v>
+        <v>454741</v>
       </c>
       <c r="R9" t="n">
-        <v>6992277</v>
+        <v>6992287</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,7 +1494,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1521,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125113775</v>
+        <v>125113719</v>
       </c>
       <c r="B10" t="n">
         <v>57635</v>
@@ -1571,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454618</v>
+        <v>454730</v>
       </c>
       <c r="R10" t="n">
-        <v>6992151</v>
+        <v>6992234</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1601,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125113720</v>
+        <v>125113721</v>
       </c>
       <c r="B11" t="n">
         <v>57635</v>
@@ -1678,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454770</v>
+        <v>454767</v>
       </c>
       <c r="R11" t="n">
-        <v>6992167</v>
+        <v>6992161</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113718</v>
+        <v>125113712</v>
       </c>
       <c r="B12" t="n">
         <v>57635</v>
@@ -1785,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454741</v>
+        <v>454510</v>
       </c>
       <c r="R12" t="n">
-        <v>6992287</v>
+        <v>6992297</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,7 +1815,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113707</v>
+        <v>125113720</v>
       </c>
       <c r="B13" t="n">
         <v>57635</v>
@@ -1892,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454599</v>
+        <v>454770</v>
       </c>
       <c r="R13" t="n">
-        <v>6992080</v>
+        <v>6992167</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1959,10 +1949,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113703</v>
+        <v>125113782</v>
       </c>
       <c r="B14" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1975,54 +1965,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Möckelåsbodarna V, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454696</v>
+        <v>454747</v>
       </c>
       <c r="R14" t="n">
-        <v>6991939</v>
+        <v>6992207</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2081,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125113780</v>
+        <v>125113716</v>
       </c>
       <c r="B15" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2097,21 +2067,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2121,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454741</v>
+        <v>454781</v>
       </c>
       <c r="R15" t="n">
-        <v>6992267</v>
+        <v>6992233</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2157,6 +2127,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2183,7 +2158,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125113709</v>
+        <v>125113775</v>
       </c>
       <c r="B16" t="n">
         <v>57635</v>
@@ -2223,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454627</v>
+        <v>454618</v>
       </c>
       <c r="R16" t="n">
-        <v>6992167</v>
+        <v>6992151</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2290,7 +2265,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125113728</v>
+        <v>125113724</v>
       </c>
       <c r="B17" t="n">
         <v>57635</v>
@@ -2330,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454803</v>
+        <v>454720</v>
       </c>
       <c r="R17" t="n">
-        <v>6991945</v>
+        <v>6992151</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,7 +2372,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125113723</v>
+        <v>125113703</v>
       </c>
       <c r="B18" t="n">
         <v>57635</v>
@@ -2430,17 +2405,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Möckelåsbodarna V, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454755</v>
+        <v>454696</v>
       </c>
       <c r="R18" t="n">
-        <v>6992152</v>
+        <v>6991939</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2473,11 +2468,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2504,10 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125113778</v>
+        <v>125113722</v>
       </c>
       <c r="B19" t="n">
-        <v>80029</v>
+        <v>57635</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2520,21 +2510,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2544,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454747</v>
+        <v>454752</v>
       </c>
       <c r="R19" t="n">
-        <v>6992205</v>
+        <v>6992152</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2580,6 +2570,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2606,7 +2601,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125113716</v>
+        <v>125113709</v>
       </c>
       <c r="B20" t="n">
         <v>57635</v>
@@ -2646,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454781</v>
+        <v>454627</v>
       </c>
       <c r="R20" t="n">
-        <v>6992233</v>
+        <v>6992167</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2686,7 +2681,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2713,7 +2708,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125113721</v>
+        <v>125113727</v>
       </c>
       <c r="B21" t="n">
         <v>57635</v>
@@ -2753,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454767</v>
+        <v>454754</v>
       </c>
       <c r="R21" t="n">
-        <v>6992161</v>
+        <v>6992018</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2820,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125113785</v>
+        <v>125113725</v>
       </c>
       <c r="B22" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2836,21 +2831,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2860,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454747</v>
+        <v>454746</v>
       </c>
       <c r="R22" t="n">
-        <v>6992042</v>
+        <v>6992129</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2896,6 +2891,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,7 +2922,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125113722</v>
+        <v>125113717</v>
       </c>
       <c r="B23" t="n">
         <v>57635</v>
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454752</v>
+        <v>454766</v>
       </c>
       <c r="R23" t="n">
-        <v>6992152</v>
+        <v>6992229</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3029,10 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125113782</v>
+        <v>125113785</v>
       </c>
       <c r="B24" t="n">
-        <v>80028</v>
+        <v>91184</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3045,21 +3045,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3072,7 +3072,7 @@
         <v>454747</v>
       </c>
       <c r="R24" t="n">
-        <v>6992207</v>
+        <v>6992042</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3131,7 +3131,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125113712</v>
+        <v>125113726</v>
       </c>
       <c r="B25" t="n">
         <v>57635</v>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454510</v>
+        <v>454737</v>
       </c>
       <c r="R25" t="n">
-        <v>6992297</v>
+        <v>6992033</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3238,7 +3238,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125113719</v>
+        <v>125113708</v>
       </c>
       <c r="B26" t="n">
         <v>57635</v>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454730</v>
+        <v>454646</v>
       </c>
       <c r="R26" t="n">
-        <v>6992234</v>
+        <v>6992125</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3345,7 +3345,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125113726</v>
+        <v>125113701</v>
       </c>
       <c r="B27" t="n">
         <v>57635</v>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454737</v>
+        <v>454753</v>
       </c>
       <c r="R27" t="n">
-        <v>6992033</v>
+        <v>6991908</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 12962-2024 artfynd.xlsx
+++ b/artfynd/A 12962-2024 artfynd.xlsx
@@ -2922,10 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125113717</v>
+        <v>125113785</v>
       </c>
       <c r="B23" t="n">
-        <v>57635</v>
+        <v>91184</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2938,21 +2938,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454766</v>
+        <v>454747</v>
       </c>
       <c r="R23" t="n">
-        <v>6992229</v>
+        <v>6992042</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2998,11 +2998,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,10 +3024,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125113785</v>
+        <v>125113717</v>
       </c>
       <c r="B24" t="n">
-        <v>91184</v>
+        <v>57635</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3045,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3069,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454747</v>
+        <v>454766</v>
       </c>
       <c r="R24" t="n">
-        <v>6992042</v>
+        <v>6992229</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3105,6 +3100,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 12962-2024 artfynd.xlsx
+++ b/artfynd/A 12962-2024 artfynd.xlsx
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125113712</v>
+        <v>125113782</v>
       </c>
       <c r="B12" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454510</v>
+        <v>454747</v>
       </c>
       <c r="R12" t="n">
-        <v>6992297</v>
+        <v>6992207</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,11 +1811,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,7 +1837,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125113720</v>
+        <v>125113712</v>
       </c>
       <c r="B13" t="n">
         <v>57635</v>
@@ -1882,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454770</v>
+        <v>454510</v>
       </c>
       <c r="R13" t="n">
-        <v>6992167</v>
+        <v>6992297</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1917,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125113782</v>
+        <v>125113720</v>
       </c>
       <c r="B14" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1989,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454747</v>
+        <v>454770</v>
       </c>
       <c r="R14" t="n">
-        <v>6992207</v>
+        <v>6992167</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,6 +2020,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 12962-2024 artfynd.xlsx
+++ b/artfynd/A 12962-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113778</v>
+        <v>125113782</v>
       </c>
       <c r="B2" t="n">
-        <v>80071</v>
+        <v>80070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,7 +713,7 @@
         <v>454747</v>
       </c>
       <c r="R2" t="n">
-        <v>6992205</v>
+        <v>6992207</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125113782</v>
+        <v>125113778</v>
       </c>
       <c r="B3" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -810,7 +810,7 @@
         <v>454747</v>
       </c>
       <c r="R3" t="n">
-        <v>6992207</v>
+        <v>6992205</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 12962-2024 artfynd.xlsx
+++ b/artfynd/A 12962-2024 artfynd.xlsx
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113775</v>
+        <v>125113717</v>
       </c>
       <c r="B6" t="n">
         <v>57651</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454618</v>
+        <v>454766</v>
       </c>
       <c r="R6" t="n">
-        <v>6992151</v>
+        <v>6992229</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,7 +1165,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125113705</v>
+        <v>125113775</v>
       </c>
       <c r="B7" t="n">
         <v>57651</v>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454690</v>
+        <v>454618</v>
       </c>
       <c r="R7" t="n">
-        <v>6991954</v>
+        <v>6992151</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,7 +1267,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125113717</v>
+        <v>125113705</v>
       </c>
       <c r="B8" t="n">
         <v>57651</v>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454766</v>
+        <v>454690</v>
       </c>
       <c r="R8" t="n">
-        <v>6992229</v>
+        <v>6991954</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 12962-2024 artfynd.xlsx
+++ b/artfynd/A 12962-2024 artfynd.xlsx
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113717</v>
+        <v>125113775</v>
       </c>
       <c r="B6" t="n">
         <v>57651</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454766</v>
+        <v>454618</v>
       </c>
       <c r="R6" t="n">
-        <v>6992229</v>
+        <v>6992151</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,7 +1165,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125113775</v>
+        <v>125113705</v>
       </c>
       <c r="B7" t="n">
         <v>57651</v>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454618</v>
+        <v>454690</v>
       </c>
       <c r="R7" t="n">
-        <v>6992151</v>
+        <v>6991954</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,7 +1267,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125113705</v>
+        <v>125113717</v>
       </c>
       <c r="B8" t="n">
         <v>57651</v>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454690</v>
+        <v>454766</v>
       </c>
       <c r="R8" t="n">
-        <v>6991954</v>
+        <v>6992229</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 12962-2024 artfynd.xlsx
+++ b/artfynd/A 12962-2024 artfynd.xlsx
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113775</v>
+        <v>125113705</v>
       </c>
       <c r="B6" t="n">
         <v>57651</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454618</v>
+        <v>454690</v>
       </c>
       <c r="R6" t="n">
-        <v>6992151</v>
+        <v>6991954</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,7 +1165,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125113705</v>
+        <v>125113775</v>
       </c>
       <c r="B7" t="n">
         <v>57651</v>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454690</v>
+        <v>454618</v>
       </c>
       <c r="R7" t="n">
-        <v>6991954</v>
+        <v>6992151</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2185,7 +2185,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125113722</v>
+        <v>125113712</v>
       </c>
       <c r="B17" t="n">
         <v>57651</v>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454752</v>
+        <v>454510</v>
       </c>
       <c r="R17" t="n">
-        <v>6992152</v>
+        <v>6992297</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2287,7 +2287,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125113712</v>
+        <v>125113722</v>
       </c>
       <c r="B18" t="n">
         <v>57651</v>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454510</v>
+        <v>454752</v>
       </c>
       <c r="R18" t="n">
-        <v>6992297</v>
+        <v>6992152</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2608,7 +2608,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125113726</v>
+        <v>125113720</v>
       </c>
       <c r="B21" t="n">
         <v>57651</v>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454737</v>
+        <v>454770</v>
       </c>
       <c r="R21" t="n">
-        <v>6992033</v>
+        <v>6992167</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2812,7 +2812,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125113720</v>
+        <v>125113706</v>
       </c>
       <c r="B23" t="n">
         <v>57651</v>
@@ -2847,10 +2847,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454770</v>
+        <v>454605</v>
       </c>
       <c r="R23" t="n">
-        <v>6992167</v>
+        <v>6992025</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2914,7 +2914,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125113706</v>
+        <v>125113726</v>
       </c>
       <c r="B24" t="n">
         <v>57651</v>
@@ -2949,10 +2949,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454605</v>
+        <v>454737</v>
       </c>
       <c r="R24" t="n">
-        <v>6992025</v>
+        <v>6992033</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 12962-2024 artfynd.xlsx
+++ b/artfynd/A 12962-2024 artfynd.xlsx
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113705</v>
+        <v>125113775</v>
       </c>
       <c r="B6" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454690</v>
+        <v>454618</v>
       </c>
       <c r="R6" t="n">
-        <v>6991954</v>
+        <v>6992151</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125113775</v>
+        <v>125113705</v>
       </c>
       <c r="B7" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454618</v>
+        <v>454690</v>
       </c>
       <c r="R7" t="n">
-        <v>6992151</v>
+        <v>6991954</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1270,7 +1270,7 @@
         <v>125113717</v>
       </c>
       <c r="B8" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>125113701</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>125113707</v>
       </c>
       <c r="B10" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>125113719</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>125113716</v>
       </c>
       <c r="B12" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>125113711</v>
       </c>
       <c r="B13" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>125113709</v>
       </c>
       <c r="B14" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>125113721</v>
       </c>
       <c r="B15" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>125113723</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2185,10 +2185,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125113712</v>
+        <v>125113722</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454510</v>
+        <v>454752</v>
       </c>
       <c r="R17" t="n">
-        <v>6992297</v>
+        <v>6992152</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2287,10 +2287,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125113722</v>
+        <v>125113712</v>
       </c>
       <c r="B18" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454752</v>
+        <v>454510</v>
       </c>
       <c r="R18" t="n">
-        <v>6992152</v>
+        <v>6992297</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2392,7 +2392,7 @@
         <v>125113703</v>
       </c>
       <c r="B19" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>125113728</v>
       </c>
       <c r="B20" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2608,10 +2608,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125113720</v>
+        <v>125113726</v>
       </c>
       <c r="B21" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454770</v>
+        <v>454737</v>
       </c>
       <c r="R21" t="n">
-        <v>6992167</v>
+        <v>6992033</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2713,7 +2713,7 @@
         <v>125113725</v>
       </c>
       <c r="B22" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2812,10 +2812,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125113706</v>
+        <v>125113720</v>
       </c>
       <c r="B23" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2847,10 +2847,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454605</v>
+        <v>454770</v>
       </c>
       <c r="R23" t="n">
-        <v>6992025</v>
+        <v>6992167</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2914,10 +2914,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125113726</v>
+        <v>125113706</v>
       </c>
       <c r="B24" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2949,10 +2949,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454737</v>
+        <v>454605</v>
       </c>
       <c r="R24" t="n">
-        <v>6992033</v>
+        <v>6992025</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3019,7 +3019,7 @@
         <v>125113708</v>
       </c>
       <c r="B25" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>125113724</v>
       </c>
       <c r="B26" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>125113727</v>
       </c>
       <c r="B27" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>125113718</v>
       </c>
       <c r="B28" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 12962-2024 artfynd.xlsx
+++ b/artfynd/A 12962-2024 artfynd.xlsx
@@ -2185,7 +2185,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125113722</v>
+        <v>125113712</v>
       </c>
       <c r="B17" t="n">
         <v>57652</v>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454752</v>
+        <v>454510</v>
       </c>
       <c r="R17" t="n">
-        <v>6992152</v>
+        <v>6992297</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2287,7 +2287,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125113712</v>
+        <v>125113722</v>
       </c>
       <c r="B18" t="n">
         <v>57652</v>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454510</v>
+        <v>454752</v>
       </c>
       <c r="R18" t="n">
-        <v>6992297</v>
+        <v>6992152</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 12962-2024 artfynd.xlsx
+++ b/artfynd/A 12962-2024 artfynd.xlsx
@@ -2185,7 +2185,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125113712</v>
+        <v>125113722</v>
       </c>
       <c r="B17" t="n">
         <v>57652</v>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454510</v>
+        <v>454752</v>
       </c>
       <c r="R17" t="n">
-        <v>6992297</v>
+        <v>6992152</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2287,7 +2287,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125113722</v>
+        <v>125113712</v>
       </c>
       <c r="B18" t="n">
         <v>57652</v>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454752</v>
+        <v>454510</v>
       </c>
       <c r="R18" t="n">
-        <v>6992152</v>
+        <v>6992297</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 12962-2024 artfynd.xlsx
+++ b/artfynd/A 12962-2024 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>125113775</v>
       </c>
       <c r="B6" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>125113705</v>
       </c>
       <c r="B7" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>125113717</v>
       </c>
       <c r="B8" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>125113701</v>
       </c>
       <c r="B9" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>125113707</v>
       </c>
       <c r="B10" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>125113719</v>
       </c>
       <c r="B11" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>125113716</v>
       </c>
       <c r="B12" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>125113711</v>
       </c>
       <c r="B13" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>125113709</v>
       </c>
       <c r="B14" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>125113721</v>
       </c>
       <c r="B15" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>125113723</v>
       </c>
       <c r="B16" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>125113722</v>
       </c>
       <c r="B17" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>125113712</v>
       </c>
       <c r="B18" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>125113703</v>
       </c>
       <c r="B19" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>125113728</v>
       </c>
       <c r="B20" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>125113726</v>
       </c>
       <c r="B21" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>125113725</v>
       </c>
       <c r="B22" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>125113720</v>
       </c>
       <c r="B23" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>125113706</v>
       </c>
       <c r="B24" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>125113708</v>
       </c>
       <c r="B25" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>125113724</v>
       </c>
       <c r="B26" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>125113727</v>
       </c>
       <c r="B27" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>125113718</v>
       </c>
       <c r="B28" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 12962-2024 artfynd.xlsx
+++ b/artfynd/A 12962-2024 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>125113775</v>
       </c>
       <c r="B6" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>125113705</v>
       </c>
       <c r="B7" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>125113717</v>
       </c>
       <c r="B8" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>125113701</v>
       </c>
       <c r="B9" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>125113707</v>
       </c>
       <c r="B10" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         <v>125113719</v>
       </c>
       <c r="B11" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>125113716</v>
       </c>
       <c r="B12" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>125113711</v>
       </c>
       <c r="B13" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>125113709</v>
       </c>
       <c r="B14" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>125113721</v>
       </c>
       <c r="B15" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>125113723</v>
       </c>
       <c r="B16" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>125113722</v>
       </c>
       <c r="B17" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>125113712</v>
       </c>
       <c r="B18" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>125113703</v>
       </c>
       <c r="B19" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         <v>125113728</v>
       </c>
       <c r="B20" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2611,7 +2611,7 @@
         <v>125113726</v>
       </c>
       <c r="B21" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>125113725</v>
       </c>
       <c r="B22" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>125113720</v>
       </c>
       <c r="B23" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>125113706</v>
       </c>
       <c r="B24" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         <v>125113708</v>
       </c>
       <c r="B25" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         <v>125113724</v>
       </c>
       <c r="B26" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         <v>125113727</v>
       </c>
       <c r="B27" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>125113718</v>
       </c>
       <c r="B28" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 12962-2024 artfynd.xlsx
+++ b/artfynd/A 12962-2024 artfynd.xlsx
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125113775</v>
+        <v>125113705</v>
       </c>
       <c r="B6" t="n">
         <v>57657</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454618</v>
+        <v>454690</v>
       </c>
       <c r="R6" t="n">
-        <v>6992151</v>
+        <v>6991954</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,7 +1165,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125113705</v>
+        <v>125113775</v>
       </c>
       <c r="B7" t="n">
         <v>57657</v>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454690</v>
+        <v>454618</v>
       </c>
       <c r="R7" t="n">
-        <v>6991954</v>
+        <v>6992151</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2185,7 +2185,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125113722</v>
+        <v>125113712</v>
       </c>
       <c r="B17" t="n">
         <v>57657</v>
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454752</v>
+        <v>454510</v>
       </c>
       <c r="R17" t="n">
-        <v>6992152</v>
+        <v>6992297</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2287,7 +2287,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125113712</v>
+        <v>125113722</v>
       </c>
       <c r="B18" t="n">
         <v>57657</v>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454510</v>
+        <v>454752</v>
       </c>
       <c r="R18" t="n">
-        <v>6992297</v>
+        <v>6992152</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2608,7 +2608,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125113726</v>
+        <v>125113720</v>
       </c>
       <c r="B21" t="n">
         <v>57657</v>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454737</v>
+        <v>454770</v>
       </c>
       <c r="R21" t="n">
-        <v>6992033</v>
+        <v>6992167</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2812,7 +2812,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125113720</v>
+        <v>125113706</v>
       </c>
       <c r="B23" t="n">
         <v>57657</v>
@@ -2847,10 +2847,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454770</v>
+        <v>454605</v>
       </c>
       <c r="R23" t="n">
-        <v>6992167</v>
+        <v>6992025</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2914,7 +2914,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125113706</v>
+        <v>125113726</v>
       </c>
       <c r="B24" t="n">
         <v>57657</v>
@@ -2949,10 +2949,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454605</v>
+        <v>454737</v>
       </c>
       <c r="R24" t="n">
-        <v>6992025</v>
+        <v>6992033</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
